--- a/output/(山本)可読性_表現適切性_再構成.xlsx
+++ b/output/(山本)可読性_表現適切性_再構成.xlsx
@@ -461,14 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>業務フロー図やUI遷移図の解説文において、ユーザを唯一の主語とし、能動態を用いた一貫性のある記述を行っている。</t>
+          <t>ユーザーの操作を定義する文書（要件定義書やユースケース記述等）において、システムではなく操作主体となるユーザーを主語とし、能動態を用いて要求事項を記述している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】ユーザがボタンを押下すると、システムは画面を遷移させ、次にユーザは入力を行う。（同一文内で操作主体と処理主体の視点が混在している）。
-→【適合例】ユーザは、スマートウォッチのボタンを押下して次画面へ遷移し、必要な情報を入力する。</t>
+【非適合例】ユーザーはスマートウォッチのアプリを起動する。その後、システムは現在位置を取得し、画面にマップを表示する。（非適合の理由：要求仕様であるにもかかわらず、後段の主語がシステムに切り替わっており、ユーザーが達成すべき目的が不明瞭となっているため。）
+→【適合例】ユーザーはスマートウォッチのアプリを起動する。その後、ユーザーは画面に表示された現在位置のマップを確認する。</t>
         </is>
       </c>
     </row>
@@ -480,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>機能仕様書や内部設計書において、システムまたは該当コンポーネントを主語とし、処理内容を統一した視点で記述している。</t>
+          <t>システム内部の振る舞いを定義する設計文書（基本設計書やAPI仕様書等）において、ユーザーの操作ではなく、システムまたは該当コンポーネントを主語とし、その責務や処理結果を記述している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】心拍数計測機能において、ユーザがセンサーに触れると数値が表示される。（設計書において動作主体がシステムではなくユーザ視点のみで記述されている）。
-→【適合例】心拍数計測機能は、センサーからの入力を検知し、算出された心拍数を画面に表示する。</t>
+【非適合例】ユーザーが測定ボタンを押すと、センサーから心拍数を取得し、結果をデータベースに保存する。（非適合の理由：コンポーネント間の連携を定義する設計文書において、処理の実行主体となるコンポーネントが明記されておらず、実装時の解釈にブレが生じるため。）
+→【適合例】心拍数計測コンポーネントは、ボタン押下イベントを受信すると、スマートウォッチのセンサーから心拍数を取得する。その後、同コンポーネントは取得したデータをデータベースに保存する。</t>
         </is>
       </c>
     </row>
@@ -499,13 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>要件定義やセキュリティ設計において、各操作の実行責任を持つアクター（ロール名）やハードウェア、ソフトウェアの名称を主語に含めている。</t>
+          <t>要件定義書や設計書に記載するすべての処理要件において、処理の実行者やアクセス権限を持つアクター（システム利用者、外部システム、内部モジュール等）を主語として明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】誰がシステムの操作権限を持っているか、文書内で特定できない。（操作権限を持つ主体が不明確である）。
-→【適合例】要件仕様書において、管理責任者がユーザのアカウント削除権限を持つことを明記している。</t>
+          <t>★新規追加
+【非適合例】承認ボタンを押下して、ワークフローを次のステータスに進行させる。（非適合の理由：操作の主体が省略されているため、誰がその操作権限を持つアクターであるかが特定できず、アクセス制御の実装要件を満たせないため。）
+→【適合例】承認権限を持つ管理担当者は、承認ボタンを押下して、ワークフローを次のステータスに進行させる。</t>
         </is>
       </c>
     </row>
@@ -517,13 +518,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>文書内に挿入されたすべての図および表に対して、一意に識別可能な通し番号（図表番号）と、内容を簡潔に示す題名（キャプション）を付与している。</t>
+          <t>文書内に挿入するすべての図表に対して、プロジェクトの文書作成標準に基づき、一意の項番および図表の主題を表すキャプションを付与している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】図表にキャプションが付いておらず、本文で参照されていない。（図表の識別情報が欠落している）。
-→【適合例】図3-1 スマートウォッチ外観図のように、図表に項番およびキャプションを付けている。</t>
+          <t>★新規追加
+【非適合例】（画像のみが貼り付けられ、タイトル表記がない状態である。）（非適合の理由：図表に項番およびキャプションが付与されておらず、本文からの参照や特定が不可能であるため。）
+→【適合例】（図表の下部にキャプションを配置する。）
+図3-1:システム全体アーキテクチャ図。</t>
         </is>
       </c>
     </row>
@@ -535,14 +538,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>本文から図表を参照する際、「下図」「上表」といった曖昧な表現を避け、図表番号を用いて指示対象を厳密に特定している。</t>
+          <t>本文中で図表に言及する際は、指示代名詞による参照を避け、該当する図表の項番を明記することで、図表と本文の対応関係を追跡可能にしている。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】下図の通り、データの流れを定義する。（複数の図がある場合にどの図を指しているか特定できない）。
-→【適合例】図4-2 データフロー図に示す通り、各処理間のデータ受け渡しを定義する。</t>
+【非適合例】システムの構成は以下の画像に示す通りである。（非適合の理由：指示代名詞のみで図表を指定しており、文書の改訂によってレイアウトが変更された際に参照先を見失うリスクがあるため。）
+→【適合例】システムの構成は、以下の「図3-1:システム全体アーキテクチャ図」に示す通りである。</t>
         </is>
       </c>
     </row>
@@ -554,13 +557,16 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>文書の論理構造に基づき、見出しレベルに応じた字下げ（インデント）や、視覚的な段落の区切りとなる行間設定を、全編を通じて統一した規約で適用している。</t>
+          <t>見出しの階層構造や本文の段落分けにおいて、プロジェクトの文書作成ガイドラインに基づき、インデントの深さと改行の位置を統一している。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】見出しと本文でインデントや改行が不統一で、読みづらい。（視覚的な構造が整理されていない）。
-→【適合例】章、節の見出しレベルに応じた字下げを行い、本文との境界に適切な空白行を挿入している。</t>
+          <t>★新規追加
+【非適合例】1.ユーザー管理機能
+ユーザーの登録を行う。（非適合の理由：見出しの直後に改行やインデントなしで本文が記載されており、視覚的な階層構造を把握できないため。）
+→【適合例】1.ユーザー管理機能
+　ユーザーの登録および削除を行う機能である。</t>
         </is>
       </c>
     </row>
@@ -572,13 +578,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>印刷時や部分的な参照時の取り違えを防止するため、全ページのヘッダーまたはフッターの定位置に、管理対象としての正式な文書名を一貫して表示している。</t>
+          <t>すべてのページのヘッダー領域に、プロジェクト定義のテンプレートに従って対象ドキュメントの正式名称およびバージョン情報を明記している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】ヘッダーに文書名が記載されていない。（印刷時などにどの文書の一部か判別できない）。
-→【適合例】全ページのヘッダーに、文書名「基本設計書」を記載している。</t>
+          <t>★新規追加
+【非適合例】（ヘッダー部分が空白のまま文書が作成されている状態である。）（非適合の理由：ヘッダーに文書名とバージョン情報が記載されておらず、印刷時やファイル分割時にどの文書の一部であるか特定できないため。）
+→【適合例】（ヘッダー部分に文書名とバージョン情報を記載する。）
+次期販売管理システム_基本設計書_v1.0。</t>
         </is>
       </c>
     </row>
@@ -590,13 +598,15 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>文書の全ページに対して、総ページ数および当該ページ番号（例：1/20）を、ページ内の統一された位置にノンブルとして付与している。</t>
+          <t>すべてのページのフッター領域に、「現在ページ数/総ページ数」の形式でノンブル（ページ番号）を記載し、文書の全体量と現在位置を特定可能にしている。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】ページ番号がない。（会議等で特定の箇所を指し示すことが困難である）。
-→【適合例】本文の各ページ下部中央に、ノンブル（ページ番号）を記載している。</t>
+          <t>★新規追加
+【非適合例】（フッター部分が空白のまま文書が作成されている状態である。）（非適合の理由：フッターにページ番号および総ページ数が記載されておらず、文書の欠落を確認できないため。）
+→【適合例】（フッター部分に総ページ数を含むページ番号を記載する。）
+-12/45-。</t>
         </is>
       </c>
     </row>
